--- a/design_tables/excel/DamageTypeConfig.xlsx
+++ b/design_tables/excel/DamageTypeConfig.xlsx
@@ -85,21 +85,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DamageTypeConfigTable" displayName="DamageTypeConfigTable" ref="A1:G9" headerRowCount="1">
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" name="id"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="hit_magic_shield"/>
-    <x:tableColumn id="4" name="hit_magic_defense"/>
-    <x:tableColumn id="5" name="hit_hp"/>
-    <x:tableColumn id="6" name="arousal_modifier"/>
-    <x:tableColumn id="7" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -469,8 +454,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc051d74a71c4603"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/design_tables/excel/DamageTypeConfig.xlsx
+++ b/design_tables/excel/DamageTypeConfig.xlsx
@@ -315,143 +315,153 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="25.5" customHeight="1">
-      <x:c r="A4" s="10" t="str">
-        <x:v>normal</x:v>
-      </x:c>
-      <x:c r="B4" s="10" t="str">
-        <x:v>普通伤害</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="E4" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="F4" s="10" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="str">
-        <x:v>按护盾、防御、生命顺序结算</x:v>
+      <x:c r="A4" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>normal</t>
+        </is>
+      </x:c>
+      <x:c r="B4" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>普通伤害</t>
+        </is>
+      </x:c>
+      <x:c r="C4" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>true</t>
+        </is>
+      </x:c>
+      <x:c r="D4" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>true</t>
+        </is>
+      </x:c>
+      <x:c r="E4" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>true</t>
+        </is>
+      </x:c>
+      <x:c r="F4" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>none</t>
+        </is>
+      </x:c>
+      <x:c r="G4" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>按护盾、防御、生命顺序结算</t>
+        </is>
       </x:c>
     </x:row>
     <x:row r="5" ht="25.5" customHeight="1">
-      <x:c r="A5" s="10" t="str">
-        <x:v>magic</x:v>
-      </x:c>
-      <x:c r="B5" s="10" t="str">
-        <x:v>魔力伤害</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="str">
-        <x:v>down</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="str">
-        <x:v>每10点发情值降低1点</x:v>
+      <x:c r="A5" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>pierce</t>
+        </is>
+      </x:c>
+      <x:c r="B5" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>穿透伤害</t>
+        </is>
+      </x:c>
+      <x:c r="C5" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>false</t>
+        </is>
+      </x:c>
+      <x:c r="D5" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>true</t>
+        </is>
+      </x:c>
+      <x:c r="E5" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>true</t>
+        </is>
+      </x:c>
+      <x:c r="F5" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>none</t>
+        </is>
+      </x:c>
+      <x:c r="G5" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>无视魔力护盾</t>
+        </is>
       </x:c>
     </x:row>
-    <x:row r="6" ht="25.5" customHeight="1">
-      <x:c r="A6" s="10" t="str">
-        <x:v>charm</x:v>
-      </x:c>
-      <x:c r="B6" s="10" t="str">
-        <x:v>魅惑伤害</x:v>
-      </x:c>
-      <x:c r="C6" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="D6" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="E6" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="F6" s="10" t="str">
-        <x:v>up</x:v>
-      </x:c>
-      <x:c r="G6" s="10" t="str">
-        <x:v>每10点发情值提升1点</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="25.5" customHeight="1">
-      <x:c r="A7" s="10" t="str">
-        <x:v>pierce</x:v>
-      </x:c>
-      <x:c r="B7" s="10" t="str">
-        <x:v>穿透伤害</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="E7" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="F7" s="10" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="G7" s="10" t="str">
-        <x:v>无视魔力护盾</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="25.5" customHeight="1">
-      <x:c r="A8" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>真实伤害</x:v>
-      </x:c>
-      <x:c r="C8" s="10" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="E8" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="F8" s="10" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="str">
-        <x:v>直接扣生命值</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="25.5" customHeight="1">
-      <x:c r="A9" s="10" t="str">
-        <x:v>shield_break</x:v>
-      </x:c>
-      <x:c r="B9" s="10" t="str">
-        <x:v>护盾破坏</x:v>
-      </x:c>
-      <x:c r="C9" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="D9" s="10" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="E9" s="10" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="F9" s="10" t="str">
-        <x:v>none</x:v>
-      </x:c>
-      <x:c r="G9" s="10" t="str">
-        <x:v>只扣魔力护盾</x:v>
-      </x:c>
-    </x:row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="6" ht="25.5" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>真实伤害</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>直接扣生命值</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="7" ht="25.5" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>shield_break</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>护盾破坏</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>只扣魔力护盾</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
